--- a/public/publications.xlsx
+++ b/public/publications.xlsx
@@ -63,7 +63,7 @@
     <t>Beyond Deterrence: Experimental Study of Factors Influencing Perceived Legitimacy and Compliance With Mandatory Vaccination</t>
   </si>
   <si>
-    <t>Horák, F., Lacko, D., Dienstbier, J.</t>
+    <t>Horák, Filip, Lacko, David, Dienstbier, Jakub</t>
   </si>
   <si>
     <t>journal-article</t>
@@ -90,7 +90,7 @@
     <t>Judicial Review of Restrictions on the Right to Conduct Business in the Czech Republic During the COVID-19 Pandemic</t>
   </si>
   <si>
-    <t>Ondřejek, P.</t>
+    <t>Ondřejek, Pavel</t>
   </si>
   <si>
     <t>European Journal of Risk Regulation</t>
@@ -115,7 +115,7 @@
     <t>Online Sharing Platforms and Copyright Protection – The Czech Unfair Competition Law Approach as a Possible Role Model?</t>
   </si>
   <si>
-    <t>Ondrejová, D.</t>
+    <t>Ondrejová, Dana</t>
   </si>
   <si>
     <t>International Review of Intellectual Property and Competition Law</t>
@@ -136,7 +136,7 @@
     <t>Long-Term Care: Not a Nightmare in the EU?</t>
   </si>
   <si>
-    <t>Koldinská, K.</t>
+    <t>Koldinská, Kristina</t>
   </si>
   <si>
     <t>book-chapter</t>
@@ -161,7 +161,7 @@
     <t>Unwritten Rules in the Czech Constitutional Law: A Functional Analysis</t>
   </si>
   <si>
-    <t>Antoš, M., Horák, F.</t>
+    <t>Antoš, Marek, Horák, Filip</t>
   </si>
   <si>
     <t>Bratislava law review</t>
@@ -186,7 +186,7 @@
     <t>Religious Neutrality and Treaty-Based Privileges: The Czech Constitutional Court on the Holy See Concordat</t>
   </si>
   <si>
-    <t xml:space="preserve">Antoš, M., Horák, F., Jelínek, F., Preuss, O. </t>
+    <t>Antoš, Marek, Horák, Filip, Jelínek, Filip, Preuss, Ondřej</t>
   </si>
   <si>
     <t>working-paper</t>
@@ -218,7 +218,7 @@
     <t>Do Migrant Shelter Hotels Cause "Native Flight"?: Evidence from NYC Housing Markets</t>
   </si>
   <si>
-    <t>LeRoy, W.</t>
+    <t>LeRoy, William</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -272,7 +272,7 @@
     <t>Macroprudential Policy and Income Inequality: The Trade-Off Between Crisis Prevention and Credit Redistribution</t>
   </si>
   <si>
-    <t>Malovaná, S., Janků, J., Hodula, M.</t>
+    <t>Malovaná, Simona, Janků, Jan, Hodula, Martin</t>
   </si>
   <si>
     <t>International Journal of Central Banking</t>
@@ -293,7 +293,7 @@
     <t>Does finance change the taste for redistribution?</t>
   </si>
   <si>
-    <t>Horváth, R., Kořínek, M., Weil, L.</t>
+    <t>Horváth, Roman, Kořínek, Matěj, Weil, Laurent</t>
   </si>
   <si>
     <t>European Journal of Political Economy</t>
@@ -317,7 +317,7 @@
     <t>Rebalancing Online Speech Regulation: A Model-Sensitive Approach to Judicial Protection of End Users in Europe</t>
   </si>
   <si>
-    <t>Hodulík, J., Jorák, F., Gangur, P.</t>
+    <t>Hodulík, Jakub, Horák, Filip, Gangur, Petr</t>
   </si>
   <si>
     <t>Information &amp; Communications Technology Law</t>
@@ -354,7 +354,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -377,11 +377,6 @@
       <sz val="11.0"/>
       <color theme="10"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -425,15 +420,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
@@ -449,10 +441,6 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -697,7 +685,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -715,533 +703,533 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>2025.0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="4">
         <v>5.0</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" ht="38.25" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>2025.0</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="4">
         <v>9.0</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="4">
         <v>1.0</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" ht="24.75" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <v>1.0</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" ht="36.0" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>2025.0</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="4">
         <v>11.0</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="4">
         <v>5.0</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="4">
         <v>5.0</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="4">
         <v>4.0</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="4">
         <v>4.0</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="4">
         <v>6.0</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="L12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>2025.0</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="4">
         <v>10.0</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="L13" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="4">
         <v>7.0</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="7" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="4">
         <v>6.0</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="L15" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="4">
         <v>6.0</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="7" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2253,4 +2241,243 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId17"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100AFF713C9B79DA84BBB0044A723BE6BDF" ma:contentTypeVersion="13" ma:contentTypeDescription="Vytvoří nový dokument" ma:contentTypeScope="" ma:versionID="680ff834b91dd261cddc2a6ee35f33d0">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2ffe165d-0c64-4cda-b671-778c29893bfb" xmlns:ns3="0575897f-d6c7-43b3-ae94-edf404cc9ee5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aacc24345174218a46a3c021031ce43a" ns2:_="" ns3:_="">
+    <xsd:import namespace="2ffe165d-0c64-4cda-b671-778c29893bfb"/>
+    <xsd:import namespace="0575897f-d6c7-43b3-ae94-edf404cc9ee5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2ffe165d-0c64-4cda-b671-778c29893bfb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Značky obrázků" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ede2c221-80ea-42f2-a6ce-7f19966b5da8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0575897f-d6c7-43b3-ae94-edf404cc9ee5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c065a697-7e04-4cff-9c49-68ede1e979d8}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0575897f-d6c7-43b3-ae94-edf404cc9ee5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Typ obsahu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Nadpis"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0575897f-d6c7-43b3-ae94-edf404cc9ee5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ffe165d-0c64-4cda-b671-778c29893bfb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{959DC94B-A723-451F-81F9-D186C74B3E6F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F792DE6-BA65-41F6-B53E-2FBBB33FAC65}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F3A6F28-72C6-407F-B9D1-CB273058F079}"/>
 </file>